--- a/水库项目出表/Template/土地分类面积汇总表.xlsx
+++ b/水库项目出表/Template/土地分类面积汇总表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sunchuanhong\Local\code\水库项目出表\Template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="360" yWindow="90" windowWidth="21840" windowHeight="12330"/>
   </bookViews>
@@ -14,10 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
-  <si>
-    <t>单位：公顷</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="101">
   <si>
     <t>功能分区</t>
   </si>
@@ -322,17 +324,21 @@
   </si>
   <si>
     <t>#水库名#项目土地分类面积汇总表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：#单位#</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,7 +391,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -417,6 +423,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -426,7 +458,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -458,18 +490,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -479,11 +520,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -525,7 +574,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -557,9 +606,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -591,6 +641,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -766,125 +817,124 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CV5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:CU5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.125" style="5" customWidth="1"/>
-    <col min="2" max="39" width="8.125" style="4" customWidth="1"/>
-    <col min="40" max="45" width="8.125" style="5" customWidth="1"/>
-    <col min="46" max="82" width="8.125" style="4" customWidth="1"/>
-    <col min="83" max="83" width="11.875" style="4" customWidth="1"/>
-    <col min="84" max="95" width="8.125" style="4" customWidth="1"/>
-    <col min="96" max="96" width="9" style="6" customWidth="1"/>
-    <col min="97" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="8.08984375" style="5" customWidth="1"/>
+    <col min="2" max="40" width="8.08984375" style="4" customWidth="1"/>
+    <col min="41" max="46" width="8.08984375" style="5" customWidth="1"/>
+    <col min="47" max="83" width="8.08984375" style="4" customWidth="1"/>
+    <col min="84" max="84" width="11.90625" style="4" customWidth="1"/>
+    <col min="85" max="94" width="8.08984375" style="4" customWidth="1"/>
+    <col min="95" max="95" width="9" style="6" customWidth="1"/>
+    <col min="96" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" s="2" customFormat="1" ht="27" customHeight="1">
-      <c r="A1" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
-      <c r="AJ1" s="13"/>
-      <c r="AK1" s="13"/>
-      <c r="AL1" s="13"/>
-      <c r="AM1" s="13"/>
-      <c r="AN1" s="13"/>
-      <c r="AO1" s="13"/>
-      <c r="AP1" s="13"/>
-      <c r="AQ1" s="13"/>
-      <c r="AR1" s="13"/>
-      <c r="AS1" s="13"/>
-      <c r="AT1" s="13"/>
-      <c r="AU1" s="13"/>
-      <c r="AV1" s="13"/>
-      <c r="AW1" s="13"/>
-      <c r="AX1" s="13"/>
-      <c r="AY1" s="13"/>
-      <c r="AZ1" s="13"/>
-      <c r="BA1" s="13"/>
-      <c r="BB1" s="13"/>
-      <c r="BC1" s="13"/>
-      <c r="BD1" s="13"/>
-      <c r="BE1" s="13"/>
-      <c r="BF1" s="13"/>
-      <c r="BG1" s="13"/>
-      <c r="BH1" s="13"/>
-      <c r="BI1" s="13"/>
-      <c r="BJ1" s="13"/>
-      <c r="BK1" s="13"/>
-      <c r="BL1" s="13"/>
-      <c r="BM1" s="13"/>
-      <c r="BN1" s="13"/>
-      <c r="BO1" s="13"/>
-      <c r="BP1" s="13"/>
-      <c r="BQ1" s="13"/>
-      <c r="BR1" s="13"/>
-      <c r="BS1" s="13"/>
-      <c r="BT1" s="13"/>
-      <c r="BU1" s="13"/>
-      <c r="BV1" s="13"/>
-      <c r="BW1" s="13"/>
-      <c r="BX1" s="13"/>
-      <c r="BY1" s="13"/>
-      <c r="BZ1" s="13"/>
-      <c r="CA1" s="13"/>
-      <c r="CB1" s="13"/>
-      <c r="CC1" s="13"/>
-      <c r="CD1" s="13"/>
-      <c r="CE1" s="13"/>
-      <c r="CF1" s="13"/>
-      <c r="CG1" s="13"/>
-      <c r="CH1" s="13"/>
-      <c r="CI1" s="13"/>
-      <c r="CJ1" s="13"/>
-      <c r="CK1" s="13"/>
-      <c r="CL1" s="13"/>
-      <c r="CM1" s="13"/>
-      <c r="CN1" s="13"/>
-      <c r="CO1" s="13"/>
-      <c r="CP1" s="13"/>
-      <c r="CQ1" s="13"/>
-      <c r="CR1" s="13"/>
-      <c r="CS1" s="13"/>
-      <c r="CT1" s="13"/>
-      <c r="CU1" s="13"/>
-      <c r="CV1" s="13"/>
+    <row r="1" spans="1:99" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="14"/>
+      <c r="AJ1" s="14"/>
+      <c r="AK1" s="14"/>
+      <c r="AL1" s="14"/>
+      <c r="AM1" s="14"/>
+      <c r="AN1" s="14"/>
+      <c r="AO1" s="14"/>
+      <c r="AP1" s="14"/>
+      <c r="AQ1" s="14"/>
+      <c r="AR1" s="14"/>
+      <c r="AS1" s="14"/>
+      <c r="AT1" s="14"/>
+      <c r="AU1" s="14"/>
+      <c r="AV1" s="14"/>
+      <c r="AW1" s="14"/>
+      <c r="AX1" s="14"/>
+      <c r="AY1" s="14"/>
+      <c r="AZ1" s="14"/>
+      <c r="BA1" s="14"/>
+      <c r="BB1" s="14"/>
+      <c r="BC1" s="14"/>
+      <c r="BD1" s="14"/>
+      <c r="BE1" s="14"/>
+      <c r="BF1" s="14"/>
+      <c r="BG1" s="14"/>
+      <c r="BH1" s="14"/>
+      <c r="BI1" s="14"/>
+      <c r="BJ1" s="14"/>
+      <c r="BK1" s="14"/>
+      <c r="BL1" s="14"/>
+      <c r="BM1" s="14"/>
+      <c r="BN1" s="14"/>
+      <c r="BO1" s="14"/>
+      <c r="BP1" s="14"/>
+      <c r="BQ1" s="14"/>
+      <c r="BR1" s="14"/>
+      <c r="BS1" s="14"/>
+      <c r="BT1" s="14"/>
+      <c r="BU1" s="14"/>
+      <c r="BV1" s="14"/>
+      <c r="BW1" s="14"/>
+      <c r="BX1" s="14"/>
+      <c r="BY1" s="14"/>
+      <c r="BZ1" s="14"/>
+      <c r="CA1" s="14"/>
+      <c r="CB1" s="14"/>
+      <c r="CC1" s="14"/>
+      <c r="CD1" s="14"/>
+      <c r="CE1" s="14"/>
+      <c r="CF1" s="14"/>
+      <c r="CG1" s="14"/>
+      <c r="CH1" s="14"/>
+      <c r="CI1" s="14"/>
+      <c r="CJ1" s="14"/>
+      <c r="CK1" s="14"/>
+      <c r="CL1" s="14"/>
+      <c r="CM1" s="14"/>
+      <c r="CN1" s="14"/>
+      <c r="CO1" s="14"/>
+      <c r="CP1" s="14"/>
+      <c r="CQ1" s="14"/>
+      <c r="CR1" s="14"/>
+      <c r="CS1" s="14"/>
+      <c r="CT1" s="14"/>
+      <c r="CU1" s="14"/>
     </row>
-    <row r="2" spans="1:100" s="2" customFormat="1" ht="13.5">
+    <row r="2" spans="1:99" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -924,13 +974,13 @@
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
       <c r="AM2" s="1"/>
-      <c r="AN2" s="3"/>
+      <c r="AN2" s="1"/>
       <c r="AO2" s="3"/>
       <c r="AP2" s="3"/>
       <c r="AQ2" s="3"/>
       <c r="AR2" s="3"/>
       <c r="AS2" s="3"/>
-      <c r="AT2" s="1"/>
+      <c r="AT2" s="3"/>
       <c r="AU2" s="1"/>
       <c r="AV2" s="1"/>
       <c r="AW2" s="1"/>
@@ -973,529 +1023,524 @@
       <c r="CH2" s="1"/>
       <c r="CI2" s="1"/>
       <c r="CJ2" s="1"/>
-      <c r="CK2" s="1"/>
+      <c r="CK2" s="9"/>
       <c r="CL2" s="9"/>
       <c r="CM2" s="9"/>
       <c r="CN2" s="9"/>
-      <c r="CO2" s="9"/>
+      <c r="CO2" s="1"/>
       <c r="CP2" s="1"/>
-      <c r="CQ2" s="1"/>
-      <c r="CS2" s="14" t="s">
+      <c r="CR2" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="CS2" s="15"/>
+      <c r="CT2" s="15"/>
+      <c r="CU2" s="15"/>
+    </row>
+    <row r="3" spans="1:99" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="CT2" s="14"/>
-      <c r="CU2" s="14"/>
-      <c r="CV2" s="14"/>
+      <c r="B3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="12"/>
+      <c r="AA3" s="12"/>
+      <c r="AB3" s="12"/>
+      <c r="AC3" s="12"/>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="12"/>
+      <c r="AF3" s="12"/>
+      <c r="AG3" s="12"/>
+      <c r="AH3" s="12"/>
+      <c r="AI3" s="12"/>
+      <c r="AJ3" s="12"/>
+      <c r="AK3" s="12"/>
+      <c r="AL3" s="12"/>
+      <c r="AM3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN3" s="12"/>
+      <c r="AO3" s="11"/>
+      <c r="AP3" s="11"/>
+      <c r="AQ3" s="11"/>
+      <c r="AR3" s="11"/>
+      <c r="AS3" s="11"/>
+      <c r="AT3" s="11"/>
+      <c r="AU3" s="12"/>
+      <c r="AV3" s="12"/>
+      <c r="AW3" s="12"/>
+      <c r="AX3" s="12"/>
+      <c r="AY3" s="12"/>
+      <c r="AZ3" s="12"/>
+      <c r="BA3" s="12"/>
+      <c r="BB3" s="12"/>
+      <c r="BC3" s="12"/>
+      <c r="BD3" s="12"/>
+      <c r="BE3" s="12"/>
+      <c r="BF3" s="12"/>
+      <c r="BG3" s="12"/>
+      <c r="BH3" s="12"/>
+      <c r="BI3" s="12"/>
+      <c r="BJ3" s="12"/>
+      <c r="BK3" s="12"/>
+      <c r="BL3" s="12"/>
+      <c r="BM3" s="12"/>
+      <c r="BN3" s="12"/>
+      <c r="BO3" s="12"/>
+      <c r="BP3" s="12"/>
+      <c r="BQ3" s="12"/>
+      <c r="BR3" s="12"/>
+      <c r="BS3" s="12"/>
+      <c r="BT3" s="12"/>
+      <c r="BU3" s="12"/>
+      <c r="BV3" s="12"/>
+      <c r="BW3" s="12"/>
+      <c r="BX3" s="12"/>
+      <c r="BY3" s="12"/>
+      <c r="BZ3" s="12"/>
+      <c r="CA3" s="12"/>
+      <c r="CB3" s="12"/>
+      <c r="CC3" s="12"/>
+      <c r="CD3" s="12"/>
+      <c r="CE3" s="12"/>
+      <c r="CF3" s="12"/>
+      <c r="CG3" s="12"/>
+      <c r="CH3" s="12"/>
+      <c r="CI3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="CJ3" s="12"/>
+      <c r="CK3" s="12"/>
+      <c r="CL3" s="12"/>
+      <c r="CM3" s="12"/>
+      <c r="CN3" s="12"/>
+      <c r="CO3" s="12"/>
+      <c r="CP3" s="12"/>
+      <c r="CQ3" s="12"/>
+      <c r="CR3" s="12"/>
+      <c r="CS3" s="12"/>
+      <c r="CT3" s="12"/>
+      <c r="CU3" s="12"/>
     </row>
-    <row r="3" spans="1:100" s="2" customFormat="1" ht="13.5">
-      <c r="A3" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="10"/>
-      <c r="AC3" s="10"/>
-      <c r="AD3" s="10"/>
-      <c r="AE3" s="10"/>
-      <c r="AF3" s="10"/>
-      <c r="AG3" s="10"/>
-      <c r="AH3" s="10"/>
-      <c r="AI3" s="10"/>
-      <c r="AJ3" s="10"/>
-      <c r="AK3" s="10"/>
-      <c r="AL3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM3" s="10"/>
-      <c r="AN3" s="12"/>
-      <c r="AO3" s="12"/>
-      <c r="AP3" s="12"/>
-      <c r="AQ3" s="12"/>
-      <c r="AR3" s="12"/>
-      <c r="AS3" s="12"/>
-      <c r="AT3" s="10"/>
-      <c r="AU3" s="10"/>
-      <c r="AV3" s="10"/>
-      <c r="AW3" s="10"/>
-      <c r="AX3" s="10"/>
-      <c r="AY3" s="10"/>
-      <c r="AZ3" s="10"/>
-      <c r="BA3" s="10"/>
-      <c r="BB3" s="10"/>
-      <c r="BC3" s="10"/>
-      <c r="BD3" s="10"/>
-      <c r="BE3" s="10"/>
-      <c r="BF3" s="10"/>
-      <c r="BG3" s="10"/>
-      <c r="BH3" s="10"/>
-      <c r="BI3" s="10"/>
-      <c r="BJ3" s="10"/>
-      <c r="BK3" s="10"/>
-      <c r="BL3" s="10"/>
-      <c r="BM3" s="10"/>
-      <c r="BN3" s="10"/>
-      <c r="BO3" s="10"/>
-      <c r="BP3" s="10"/>
-      <c r="BQ3" s="10"/>
-      <c r="BR3" s="10"/>
-      <c r="BS3" s="10"/>
-      <c r="BT3" s="10"/>
-      <c r="BU3" s="10"/>
-      <c r="BV3" s="10"/>
-      <c r="BW3" s="10"/>
-      <c r="BX3" s="10"/>
-      <c r="BY3" s="10"/>
-      <c r="BZ3" s="10"/>
-      <c r="CA3" s="10"/>
-      <c r="CB3" s="10"/>
-      <c r="CC3" s="10"/>
-      <c r="CD3" s="10"/>
-      <c r="CE3" s="10"/>
-      <c r="CF3" s="10"/>
-      <c r="CG3" s="10"/>
-      <c r="CH3" s="10" t="s">
+    <row r="4" spans="1:99" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.25">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="CI3" s="10"/>
-      <c r="CJ3" s="10"/>
-      <c r="CK3" s="10"/>
-      <c r="CL3" s="10"/>
-      <c r="CM3" s="10"/>
-      <c r="CN3" s="10"/>
-      <c r="CO3" s="10"/>
-      <c r="CP3" s="10"/>
-      <c r="CQ3" s="10"/>
-      <c r="CR3" s="10"/>
-      <c r="CS3" s="10"/>
-      <c r="CT3" s="10"/>
-      <c r="CU3" s="10"/>
-      <c r="CV3" s="10"/>
+      <c r="J4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="11"/>
+      <c r="AE4" s="11"/>
+      <c r="AF4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="AN4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="BB4" s="11"/>
+      <c r="BC4" s="11"/>
+      <c r="BD4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="BE4" s="11"/>
+      <c r="BF4" s="11"/>
+      <c r="BG4" s="11"/>
+      <c r="BH4" s="11"/>
+      <c r="BI4" s="11"/>
+      <c r="BJ4" s="11"/>
+      <c r="BK4" s="11"/>
+      <c r="BL4" s="11"/>
+      <c r="BM4" s="11"/>
+      <c r="BN4" s="11"/>
+      <c r="BO4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="BP4" s="11"/>
+      <c r="BQ4" s="11"/>
+      <c r="BR4" s="11"/>
+      <c r="BS4" s="11"/>
+      <c r="BT4" s="11"/>
+      <c r="BU4" s="11"/>
+      <c r="BV4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="BW4" s="11"/>
+      <c r="BX4" s="11"/>
+      <c r="BY4" s="11"/>
+      <c r="BZ4" s="11"/>
+      <c r="CA4" s="11"/>
+      <c r="CB4" s="11"/>
+      <c r="CC4" s="11"/>
+      <c r="CD4" s="11"/>
+      <c r="CE4" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="CF4" s="12"/>
+      <c r="CG4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="CH4" s="12"/>
+      <c r="CI4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="CJ4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="CK4" s="11"/>
+      <c r="CL4" s="11"/>
+      <c r="CM4" s="11"/>
+      <c r="CN4" s="11"/>
+      <c r="CO4" s="11"/>
+      <c r="CP4" s="11"/>
+      <c r="CQ4" s="11"/>
+      <c r="CR4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="CS4" s="11"/>
+      <c r="CT4" s="11"/>
+      <c r="CU4" s="11"/>
     </row>
-    <row r="4" spans="1:100" s="2" customFormat="1" ht="13.5">
-      <c r="A4" s="12"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12"/>
-      <c r="AH4" s="12"/>
-      <c r="AI4" s="12"/>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="12"/>
-      <c r="AL4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM4" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AN4" s="12"/>
-      <c r="AO4" s="12"/>
-      <c r="AP4" s="12"/>
-      <c r="AQ4" s="12"/>
-      <c r="AR4" s="12"/>
-      <c r="AS4" s="12"/>
-      <c r="AT4" s="12"/>
-      <c r="AU4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV4" s="12"/>
-      <c r="AW4" s="12"/>
-      <c r="AX4" s="12"/>
-      <c r="AY4" s="12"/>
-      <c r="AZ4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="BA4" s="12"/>
-      <c r="BB4" s="12"/>
-      <c r="BC4" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="BD4" s="12"/>
-      <c r="BE4" s="12"/>
-      <c r="BF4" s="12"/>
-      <c r="BG4" s="12"/>
-      <c r="BH4" s="12"/>
-      <c r="BI4" s="12"/>
-      <c r="BJ4" s="12"/>
-      <c r="BK4" s="12"/>
-      <c r="BL4" s="12"/>
-      <c r="BM4" s="12"/>
-      <c r="BN4" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="BO4" s="12"/>
-      <c r="BP4" s="12"/>
-      <c r="BQ4" s="12"/>
-      <c r="BR4" s="12"/>
-      <c r="BS4" s="12"/>
-      <c r="BT4" s="12"/>
-      <c r="BU4" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="BV4" s="12"/>
-      <c r="BW4" s="12"/>
-      <c r="BX4" s="12"/>
-      <c r="BY4" s="12"/>
-      <c r="BZ4" s="12"/>
-      <c r="CA4" s="12"/>
-      <c r="CB4" s="12"/>
-      <c r="CC4" s="12"/>
-      <c r="CD4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="CE4" s="10"/>
-      <c r="CF4" s="10" t="s">
+    <row r="5" spans="1:99" s="2" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="CG4" s="10"/>
-      <c r="CH4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="CI4" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="CJ4" s="10"/>
-      <c r="CK4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="CL4" s="12"/>
-      <c r="CM4" s="12"/>
-      <c r="CN4" s="12"/>
-      <c r="CO4" s="12"/>
-      <c r="CP4" s="12"/>
-      <c r="CQ4" s="12"/>
-      <c r="CR4" s="12"/>
-      <c r="CS4" s="12" t="s">
+      <c r="K5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="CT4" s="12"/>
-      <c r="CU4" s="12"/>
-      <c r="CV4" s="12"/>
-    </row>
-    <row r="5" spans="1:100" s="2" customFormat="1" ht="33.75">
-      <c r="A5" s="12"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" s="8" t="s">
+      <c r="O5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="N5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="8" t="s">
+      <c r="P5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="Q5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="R5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="S5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="T5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="T5" s="8" t="s">
+      <c r="U5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="U5" s="8" t="s">
+      <c r="V5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="V5" s="8" t="s">
+      <c r="W5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="W5" s="8" t="s">
+      <c r="X5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="X5" s="8" t="s">
+      <c r="Y5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="Z5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="Z5" s="8" t="s">
+      <c r="AA5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="AA5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB5" s="8" t="s">
+      <c r="AC5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="AC5" s="8" t="s">
+      <c r="AD5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="AD5" s="8" t="s">
+      <c r="AE5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="AE5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF5" s="8" t="s">
+      <c r="AH5" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="AG5" s="8" t="s">
+      <c r="AI5" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AH5" s="8" t="s">
+      <c r="AJ5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="AI5" s="8" t="s">
+      <c r="AK5" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="AJ5" s="8" t="s">
+      <c r="AL5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="AK5" s="8" t="s">
+      <c r="AM5" s="17"/>
+      <c r="AN5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AL5" s="10"/>
-      <c r="AM5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN5" s="8" t="s">
+      <c r="AP5" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="AO5" s="8" t="s">
+      <c r="AQ5" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="AP5" s="8" t="s">
+      <c r="AR5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="AQ5" s="8" t="s">
+      <c r="AS5" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="AR5" s="8" t="s">
+      <c r="AT5" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="AS5" s="8" t="s">
+      <c r="AU5" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="AT5" s="8" t="s">
+      <c r="AV5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="AW5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="AU5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AV5" s="8" t="s">
+      <c r="AX5" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="AW5" s="8" t="s">
+      <c r="AY5" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="AX5" s="8" t="s">
+      <c r="AZ5" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="AY5" s="8" t="s">
+      <c r="BA5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="BB5" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="AZ5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="BA5" s="8" t="s">
+      <c r="BC5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="BB5" s="8" t="s">
+      <c r="BD5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="BE5" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="BC5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="BD5" s="8" t="s">
+      <c r="BF5" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="BE5" s="8" t="s">
+      <c r="BG5" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="BF5" s="8" t="s">
+      <c r="BH5" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="BG5" s="8" t="s">
+      <c r="BI5" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="BH5" s="8" t="s">
+      <c r="BJ5" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="BI5" s="8" t="s">
+      <c r="BK5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="BJ5" s="8" t="s">
+      <c r="BL5" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="BK5" s="8" t="s">
+      <c r="BM5" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="BL5" s="8" t="s">
+      <c r="BN5" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="BM5" s="8" t="s">
+      <c r="BO5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="BP5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="BN5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="BO5" s="8" t="s">
+      <c r="BQ5" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="BP5" s="8" t="s">
+      <c r="BR5" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="BQ5" s="8" t="s">
+      <c r="BS5" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="BR5" s="8" t="s">
+      <c r="BT5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="BS5" s="8" t="s">
+      <c r="BU5" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="BT5" s="8" t="s">
+      <c r="BV5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="BW5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="BU5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="BV5" s="8" t="s">
+      <c r="BX5" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="BW5" s="8" t="s">
+      <c r="BY5" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="BX5" s="8" t="s">
+      <c r="BZ5" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="BY5" s="8" t="s">
+      <c r="CA5" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="BZ5" s="8" t="s">
+      <c r="CB5" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="CA5" s="8" t="s">
+      <c r="CC5" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="CB5" s="8" t="s">
+      <c r="CD5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="CC5" s="8" t="s">
+      <c r="CE5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="CF5" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="CD5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="CE5" s="8" t="s">
+      <c r="CG5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="CH5" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="CF5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="CG5" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="CH5" s="10"/>
-      <c r="CI5" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="CI5" s="17"/>
       <c r="CJ5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="CK5" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="CK5" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="CL5" s="8" t="s">
         <v>90</v>
@@ -1516,10 +1561,10 @@
         <v>95</v>
       </c>
       <c r="CR5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="CS5" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="CS5" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="CT5" s="8" t="s">
         <v>97</v>
@@ -1527,39 +1572,35 @@
       <c r="CU5" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="CV5" s="8" t="s">
-        <v>99</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="CK4:CR4"/>
-    <mergeCell ref="BU4:CC4"/>
-    <mergeCell ref="CD4:CE4"/>
-    <mergeCell ref="CF4:CG4"/>
-    <mergeCell ref="CH4:CH5"/>
-    <mergeCell ref="CI4:CJ4"/>
-    <mergeCell ref="AM4:AT4"/>
-    <mergeCell ref="AU4:AY4"/>
-    <mergeCell ref="AZ4:BB4"/>
-    <mergeCell ref="BC4:BM4"/>
-    <mergeCell ref="BN4:BT4"/>
+  <mergeCells count="31">
+    <mergeCell ref="CJ4:CQ4"/>
+    <mergeCell ref="BV4:CD4"/>
+    <mergeCell ref="CE4:CF4"/>
+    <mergeCell ref="CG4:CH4"/>
+    <mergeCell ref="CI4:CI5"/>
+    <mergeCell ref="AN4:AU4"/>
+    <mergeCell ref="AV4:AZ4"/>
+    <mergeCell ref="BA4:BC4"/>
+    <mergeCell ref="BD4:BN4"/>
+    <mergeCell ref="BO4:BU4"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="G3:G5"/>
     <mergeCell ref="H3:H5"/>
-    <mergeCell ref="A1:CV1"/>
-    <mergeCell ref="CS2:CV2"/>
-    <mergeCell ref="I3:AK3"/>
-    <mergeCell ref="AL3:CG3"/>
-    <mergeCell ref="CH3:CV3"/>
+    <mergeCell ref="A1:CU1"/>
+    <mergeCell ref="CR2:CU2"/>
+    <mergeCell ref="I3:AL3"/>
+    <mergeCell ref="AM3:CH3"/>
+    <mergeCell ref="CI3:CU3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:M4"/>
     <mergeCell ref="N4:R4"/>
     <mergeCell ref="S4:Z4"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="AE4:AK4"/>
-    <mergeCell ref="AL4:AL5"/>
-    <mergeCell ref="CS4:CV4"/>
+    <mergeCell ref="AA4:AE4"/>
+    <mergeCell ref="AF4:AL4"/>
+    <mergeCell ref="AM4:AM5"/>
+    <mergeCell ref="CR4:CU4"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
